--- a/标准模版/小企业会计准则/资产负债表.xlsx
+++ b/标准模版/小企业会计准则/资产负债表.xlsx
@@ -1,33 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView showSheetTabs="0" windowHeight="17655"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25000" windowHeight="17655"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet2" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
-    <sheet name="BB000.VTS" sheetId="3" r:id="rId3"/>
+    <sheet sheetId="1" name="Sheet2" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Sheet1" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="BB000.VTS" state="visible" r:id="rId6"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">#N/A</definedName>
-  </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
@@ -532,424 +516,81 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="#,##0.00_);[Red]\(#,##0.00\)"/>
-    <numFmt numFmtId="177" formatCode="#,##0.00&quot;￥&quot;;[Red]\-#,##0.00&quot;￥&quot;"/>
-    <numFmt numFmtId="178" formatCode="#,##0_);[Red]\(#,##0\)"/>
-    <numFmt numFmtId="179" formatCode="#,##0&quot;￥&quot;;[Red]\-#,##0&quot;￥&quot;"/>
-    <numFmt numFmtId="180" formatCode="#,##0.00;\-#,##0.00;#"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0.00;-#,##0.00;#"/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
-      <color indexed="8"/>
-      <name val="Arial"/>
-      <charset val="0"/>
+      <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
+      <charset val="134"/>
+      <color indexed="8"/>
       <sz val="12"/>
-      <color indexed="8"/>
       <name val="宋体"/>
-      <charset val="134"/>
     </font>
     <font>
       <b/>
+      <charset val="134"/>
       <sz val="24"/>
       <name val="宋体"/>
-      <charset val="134"/>
     </font>
     <font>
+      <charset val="134"/>
       <sz val="11"/>
       <name val="宋体"/>
-      <charset val="134"/>
     </font>
     <font>
       <b/>
+      <charset val="134"/>
       <sz val="12"/>
       <name val="宋体"/>
-      <charset val="134"/>
     </font>
     <font>
       <b/>
+      <charset val="134"/>
       <sz val="10"/>
       <name val="宋体"/>
+    </font>
+    <font>
       <charset val="134"/>
+      <sz val="12"/>
+      <name val="宋体"/>
+    </font>
+    <font>
+      <charset val="134"/>
+      <sz val="10"/>
+      <name val="宋体"/>
+    </font>
+    <font>
+      <color indexed="8"/>
+      <sz val="12"/>
+      <name val="Arial"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <name val="Arial"/>
-      <charset val="0"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color indexed="8"/>
-      <name val="MS Sans Serif"/>
-      <charset val="0"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="25">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -958,850 +599,249 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="medium"/>
+      <right style="thin"/>
+      <top style="medium"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="medium"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="medium"/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
+      <left style="thin"/>
+      <right style="medium"/>
+      <top style="medium"/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="medium"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
+      <left style="thin"/>
       <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="medium"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
+      <left style="thin"/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
+      <left style="medium"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="medium"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="medium"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="medium"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="medium"/>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
+      <top style="thin"/>
+      <bottom style="medium"/>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="medium"/>
+      <top style="thin"/>
+      <bottom style="medium"/>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="177" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="179" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="17" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="180" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="180" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="5" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="17">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="double">
-          <color theme="4"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <left style="thin">
-          <color theme="4"/>
-        </left>
-        <right style="thin">
-          <color theme="4"/>
-        </right>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-        <horizontal style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-  </dxfs>
-  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
-    </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
-    </tableStyle>
-  </tableStyles>
-  <colors>
-    <mruColors>
-      <color rgb="00000000"/>
-    </mruColors>
-  </colors>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2063,12 +1103,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I41"/>
-  <sheetFormatPr defaultColWidth="9.14814814814815" defaultRowHeight="21.6" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="21" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="9.14814814814815" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="21.1111111111111" customWidth="1"/>
     <col min="2" max="2" width="3.44444444444444" customWidth="1"/>
@@ -2079,7 +1119,7 @@
     <col min="9" max="16384" width="9.14814814814815" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="7.5" customHeight="1" spans="1:9">
+    <row r="1" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2089,35 +1129,35 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
     </row>
-    <row r="2" ht="48" customHeight="1" spans="1:9">
-      <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-    </row>
-    <row r="3" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A3" s="5" t="s">
+    <row r="2" ht="21" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+    </row>
+    <row r="3" ht="21" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="5" t="s">
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="7" t="s">
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="6" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" ht="12" customHeight="1" spans="1:9">
+    <row r="4" ht="21" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -2127,62 +1167,62 @@
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" ht="36.7" customHeight="1" spans="1:9">
-      <c r="A5" s="8" t="s">
+    <row r="5" ht="21" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="E5" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="10" t="s">
+      <c r="G5" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="12" t="s">
+      <c r="H5" s="11" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="1:9">
-      <c r="A6" s="13" t="s">
+    <row r="6" ht="21" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="14"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="16" t="s">
+      <c r="B6" s="13"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="14"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="17"/>
-      <c r="I6" s="44"/>
-    </row>
-    <row r="7" customHeight="1" spans="1:9">
+      <c r="F6" s="13"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="17"/>
+    </row>
+    <row r="7" ht="21" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="18" t="s">
         <v>13</v>
       </c>
       <c r="B7" s="19">
         <v>1</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="C7" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="15" t="s">
+      <c r="D7" s="14" t="s">
         <v>15</v>
       </c>
       <c r="E7" s="20" t="s">
@@ -2191,25 +1231,25 @@
       <c r="F7" s="19">
         <v>33</v>
       </c>
-      <c r="G7" s="15" t="s">
+      <c r="G7" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="H7" s="17" t="s">
+      <c r="H7" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="I7" s="44"/>
-    </row>
-    <row r="8" customHeight="1" spans="1:9">
+      <c r="I7" s="17"/>
+    </row>
+    <row r="8" ht="21" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="18" t="s">
         <v>19</v>
       </c>
       <c r="B8" s="19">
         <v>2</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="C8" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="15" t="s">
+      <c r="D8" s="14" t="s">
         <v>21</v>
       </c>
       <c r="E8" s="20" t="s">
@@ -2218,25 +1258,25 @@
       <c r="F8" s="19">
         <v>34</v>
       </c>
-      <c r="G8" s="15" t="s">
+      <c r="G8" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="H8" s="17" t="s">
+      <c r="H8" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="I8" s="44"/>
-    </row>
-    <row r="9" customHeight="1" spans="1:9">
+      <c r="I8" s="17"/>
+    </row>
+    <row r="9" ht="21" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="18" t="s">
         <v>25</v>
       </c>
       <c r="B9" s="19">
         <v>3</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="C9" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="15" t="s">
+      <c r="D9" s="14" t="s">
         <v>27</v>
       </c>
       <c r="E9" s="20" t="s">
@@ -2245,25 +1285,25 @@
       <c r="F9" s="19">
         <v>35</v>
       </c>
-      <c r="G9" s="15" t="s">
+      <c r="G9" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="H9" s="17" t="s">
+      <c r="H9" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="I9" s="44"/>
-    </row>
-    <row r="10" customHeight="1" spans="1:9">
+      <c r="I9" s="17"/>
+    </row>
+    <row r="10" ht="21" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="18" t="s">
         <v>31</v>
       </c>
       <c r="B10" s="19">
         <v>4</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="C10" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="D10" s="15" t="s">
+      <c r="D10" s="14" t="s">
         <v>33</v>
       </c>
       <c r="E10" s="20" t="s">
@@ -2272,25 +1312,25 @@
       <c r="F10" s="19">
         <v>36</v>
       </c>
-      <c r="G10" s="15" t="s">
+      <c r="G10" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="H10" s="17" t="s">
+      <c r="H10" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="I10" s="44"/>
-    </row>
-    <row r="11" customHeight="1" spans="1:9">
+      <c r="I10" s="17"/>
+    </row>
+    <row r="11" ht="21" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="18" t="s">
         <v>37</v>
       </c>
       <c r="B11" s="19">
         <v>5</v>
       </c>
-      <c r="C11" s="15" t="s">
+      <c r="C11" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="D11" s="15" t="s">
+      <c r="D11" s="14" t="s">
         <v>39</v>
       </c>
       <c r="E11" s="20" t="s">
@@ -2299,25 +1339,25 @@
       <c r="F11" s="19">
         <v>37</v>
       </c>
-      <c r="G11" s="15" t="s">
+      <c r="G11" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="H11" s="17" t="s">
+      <c r="H11" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="I11" s="44"/>
-    </row>
-    <row r="12" customHeight="1" spans="1:9">
+      <c r="I11" s="17"/>
+    </row>
+    <row r="12" ht="21" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="18" t="s">
         <v>43</v>
       </c>
       <c r="B12" s="19">
         <v>6</v>
       </c>
-      <c r="C12" s="15" t="s">
+      <c r="C12" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="D12" s="15" t="s">
+      <c r="D12" s="14" t="s">
         <v>45</v>
       </c>
       <c r="E12" s="20" t="s">
@@ -2326,25 +1366,25 @@
       <c r="F12" s="19">
         <v>38</v>
       </c>
-      <c r="G12" s="15" t="s">
+      <c r="G12" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="H12" s="17" t="s">
+      <c r="H12" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="I12" s="44"/>
-    </row>
-    <row r="13" customHeight="1" spans="1:9">
+      <c r="I12" s="17"/>
+    </row>
+    <row r="13" ht="21" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
         <v>49</v>
       </c>
       <c r="B13" s="19">
         <v>7</v>
       </c>
-      <c r="C13" s="15" t="s">
+      <c r="C13" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="D13" s="14" t="s">
         <v>51</v>
       </c>
       <c r="E13" s="20" t="s">
@@ -2353,25 +1393,25 @@
       <c r="F13" s="19">
         <v>39</v>
       </c>
-      <c r="G13" s="15" t="s">
+      <c r="G13" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="H13" s="17" t="s">
+      <c r="H13" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="I13" s="44"/>
-    </row>
-    <row r="14" customHeight="1" spans="1:9">
+      <c r="I13" s="17"/>
+    </row>
+    <row r="14" ht="21" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="18" t="s">
         <v>55</v>
       </c>
       <c r="B14" s="19">
         <v>8</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="C14" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="D14" s="15" t="s">
+      <c r="D14" s="14" t="s">
         <v>57</v>
       </c>
       <c r="E14" s="20" t="s">
@@ -2380,25 +1420,25 @@
       <c r="F14" s="19">
         <v>40</v>
       </c>
-      <c r="G14" s="15" t="s">
+      <c r="G14" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="H14" s="17" t="s">
+      <c r="H14" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="I14" s="44"/>
-    </row>
-    <row r="15" customHeight="1" spans="1:9">
+      <c r="I14" s="17"/>
+    </row>
+    <row r="15" ht="21" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="s">
         <v>61</v>
       </c>
       <c r="B15" s="19">
         <v>9</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="C15" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="D15" s="15" t="s">
+      <c r="D15" s="14" t="s">
         <v>63</v>
       </c>
       <c r="E15" s="20" t="s">
@@ -2407,25 +1447,25 @@
       <c r="F15" s="19">
         <v>41</v>
       </c>
-      <c r="G15" s="15" t="s">
+      <c r="G15" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="H15" s="17" t="s">
+      <c r="H15" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="I15" s="44"/>
-    </row>
-    <row r="16" customHeight="1" spans="1:9">
+      <c r="I15" s="17"/>
+    </row>
+    <row r="16" ht="21" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="18" t="s">
         <v>67</v>
       </c>
       <c r="B16" s="19">
         <v>10</v>
       </c>
-      <c r="C16" s="15" t="s">
+      <c r="C16" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="D16" s="15" t="s">
+      <c r="D16" s="14" t="s">
         <v>69</v>
       </c>
       <c r="E16" s="20" t="s">
@@ -2434,42 +1474,42 @@
       <c r="F16" s="19">
         <v>42</v>
       </c>
-      <c r="G16" s="15"/>
-      <c r="H16" s="17"/>
-      <c r="I16" s="44"/>
-    </row>
-    <row r="17" customHeight="1" spans="1:9">
+      <c r="G16" s="14"/>
+      <c r="H16" s="16"/>
+      <c r="I16" s="17"/>
+    </row>
+    <row r="17" ht="21" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="18" t="s">
         <v>71</v>
       </c>
       <c r="B17" s="19">
         <v>11</v>
       </c>
-      <c r="C17" s="15" t="s">
+      <c r="C17" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="D17" s="15" t="s">
+      <c r="D17" s="14" t="s">
         <v>73</v>
       </c>
       <c r="E17" s="21"/>
       <c r="F17" s="19">
         <v>43</v>
       </c>
-      <c r="G17" s="15"/>
-      <c r="H17" s="17"/>
-      <c r="I17" s="44"/>
-    </row>
-    <row r="18" customHeight="1" spans="1:9">
+      <c r="G17" s="14"/>
+      <c r="H17" s="16"/>
+      <c r="I17" s="17"/>
+    </row>
+    <row r="18" ht="21" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="18" t="s">
         <v>74</v>
       </c>
       <c r="B18" s="19">
         <v>12</v>
       </c>
-      <c r="C18" s="15" t="s">
+      <c r="C18" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="D18" s="15" t="s">
+      <c r="D18" s="14" t="s">
         <v>76</v>
       </c>
       <c r="E18" s="22" t="s">
@@ -2486,42 +1526,42 @@
         <f>SUM(H7:H16)</f>
         <v>0</v>
       </c>
-      <c r="I18" s="44"/>
-    </row>
-    <row r="19" customHeight="1" spans="1:9">
+      <c r="I18" s="17"/>
+    </row>
+    <row r="19" ht="21" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="18" t="s">
         <v>78</v>
       </c>
       <c r="B19" s="19">
         <v>13</v>
       </c>
-      <c r="C19" s="15" t="s">
+      <c r="C19" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="D19" s="15" t="s">
+      <c r="D19" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="E19" s="16" t="s">
+      <c r="E19" s="15" t="s">
         <v>81</v>
       </c>
       <c r="F19" s="19">
         <v>45</v>
       </c>
-      <c r="G19" s="15"/>
-      <c r="H19" s="17"/>
-      <c r="I19" s="44"/>
-    </row>
-    <row r="20" customHeight="1" spans="1:9">
+      <c r="G19" s="14"/>
+      <c r="H19" s="16"/>
+      <c r="I19" s="17"/>
+    </row>
+    <row r="20" ht="21" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="18" t="s">
         <v>82</v>
       </c>
       <c r="B20" s="19">
         <v>14</v>
       </c>
-      <c r="C20" s="15" t="s">
+      <c r="C20" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="D20" s="15" t="s">
+      <c r="D20" s="14" t="s">
         <v>84</v>
       </c>
       <c r="E20" s="20" t="s">
@@ -2530,15 +1570,15 @@
       <c r="F20" s="19">
         <v>46</v>
       </c>
-      <c r="G20" s="15" t="s">
+      <c r="G20" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="H20" s="17" t="s">
+      <c r="H20" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="I20" s="44"/>
-    </row>
-    <row r="21" customHeight="1" spans="1:9">
+      <c r="I20" s="17"/>
+    </row>
+    <row r="21" ht="21" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="24" t="s">
         <v>85</v>
       </c>
@@ -2559,44 +1599,44 @@
       <c r="F21" s="19">
         <v>47</v>
       </c>
-      <c r="G21" s="15" t="s">
+      <c r="G21" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="H21" s="17" t="s">
+      <c r="H21" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="I21" s="44"/>
-    </row>
-    <row r="22" customHeight="1" spans="1:9">
-      <c r="A22" s="13" t="s">
+      <c r="I21" s="17"/>
+    </row>
+    <row r="22" ht="21" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" s="12" t="s">
         <v>86</v>
       </c>
       <c r="B22" s="19">
         <v>16</v>
       </c>
-      <c r="C22" s="15"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="16" t="s">
+      <c r="C22" s="14"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="15" t="s">
         <v>87</v>
       </c>
       <c r="F22" s="19">
         <v>48</v>
       </c>
-      <c r="G22" s="15"/>
-      <c r="H22" s="17"/>
-      <c r="I22" s="44"/>
-    </row>
-    <row r="23" customHeight="1" spans="1:9">
+      <c r="G22" s="14"/>
+      <c r="H22" s="16"/>
+      <c r="I22" s="17"/>
+    </row>
+    <row r="23" ht="21" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="18" t="s">
         <v>88</v>
       </c>
       <c r="B23" s="19">
         <v>17</v>
       </c>
-      <c r="C23" s="15" t="s">
+      <c r="C23" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="D23" s="15" t="s">
+      <c r="D23" s="14" t="s">
         <v>90</v>
       </c>
       <c r="E23" s="20" t="s">
@@ -2605,25 +1645,25 @@
       <c r="F23" s="19">
         <v>49</v>
       </c>
-      <c r="G23" s="15" t="s">
+      <c r="G23" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="H23" s="17" t="s">
+      <c r="H23" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="I23" s="44"/>
-    </row>
-    <row r="24" customHeight="1" spans="1:9">
+      <c r="I23" s="17"/>
+    </row>
+    <row r="24" ht="21" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="18" t="s">
         <v>94</v>
       </c>
       <c r="B24" s="19">
         <v>18</v>
       </c>
-      <c r="C24" s="15" t="s">
+      <c r="C24" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="D24" s="15" t="s">
+      <c r="D24" s="14" t="s">
         <v>96</v>
       </c>
       <c r="E24" s="20" t="s">
@@ -2632,25 +1672,25 @@
       <c r="F24" s="19">
         <v>50</v>
       </c>
-      <c r="G24" s="15" t="s">
+      <c r="G24" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="H24" s="17" t="s">
+      <c r="H24" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="I24" s="44"/>
-    </row>
-    <row r="25" customHeight="1" spans="1:9">
+      <c r="I24" s="17"/>
+    </row>
+    <row r="25" ht="21" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="18" t="s">
         <v>100</v>
       </c>
       <c r="B25" s="19">
         <v>19</v>
       </c>
-      <c r="C25" s="15" t="s">
+      <c r="C25" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="D25" s="15" t="s">
+      <c r="D25" s="14" t="s">
         <v>102</v>
       </c>
       <c r="E25" s="20" t="s">
@@ -2659,25 +1699,25 @@
       <c r="F25" s="19">
         <v>51</v>
       </c>
-      <c r="G25" s="15" t="s">
+      <c r="G25" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="H25" s="17" t="s">
+      <c r="H25" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="I25" s="44"/>
-    </row>
-    <row r="26" customHeight="1" spans="1:9">
+      <c r="I25" s="17"/>
+    </row>
+    <row r="26" ht="21" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="18" t="s">
         <v>106</v>
       </c>
       <c r="B26" s="19">
         <v>20</v>
       </c>
-      <c r="C26" s="15" t="s">
+      <c r="C26" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="D26" s="15" t="s">
+      <c r="D26" s="14" t="s">
         <v>108</v>
       </c>
       <c r="E26" s="20" t="s">
@@ -2686,22 +1726,22 @@
       <c r="F26" s="19">
         <v>52</v>
       </c>
-      <c r="G26" s="15"/>
-      <c r="H26" s="17"/>
-      <c r="I26" s="44"/>
-    </row>
-    <row r="27" customHeight="1" spans="1:9">
+      <c r="G26" s="14"/>
+      <c r="H26" s="16"/>
+      <c r="I26" s="17"/>
+    </row>
+    <row r="27" ht="21" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="18" t="s">
         <v>110</v>
       </c>
       <c r="B27" s="19">
         <v>21</v>
       </c>
-      <c r="C27" s="15" t="e">
+      <c r="C27" s="14" t="e">
         <f>C25-C26</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D27" s="15" t="e">
+      <c r="D27" s="14" t="e">
         <f>D25-D26</f>
         <v>#VALUE!</v>
       </c>
@@ -2711,19 +1751,19 @@
       </c>
       <c r="G27" s="25"/>
       <c r="H27" s="26"/>
-      <c r="I27" s="44"/>
-    </row>
-    <row r="28" customHeight="1" spans="1:9">
+      <c r="I27" s="17"/>
+    </row>
+    <row r="28" ht="21" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="18" t="s">
         <v>111</v>
       </c>
       <c r="B28" s="19">
         <v>22</v>
       </c>
-      <c r="C28" s="15" t="s">
+      <c r="C28" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="D28" s="15" t="s">
+      <c r="D28" s="14" t="s">
         <v>113</v>
       </c>
       <c r="E28" s="22" t="s">
@@ -2740,19 +1780,19 @@
         <f>SUM(H23:H26)</f>
         <v>0</v>
       </c>
-      <c r="I28" s="44"/>
-    </row>
-    <row r="29" customHeight="1" spans="1:9">
+      <c r="I28" s="17"/>
+    </row>
+    <row r="29" ht="21" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="18" t="s">
         <v>115</v>
       </c>
       <c r="B29" s="19">
         <v>23</v>
       </c>
-      <c r="C29" s="15" t="s">
+      <c r="C29" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="D29" s="15" t="s">
+      <c r="D29" s="14" t="s">
         <v>117</v>
       </c>
       <c r="E29" s="22" t="s">
@@ -2769,65 +1809,65 @@
         <f>H18+H28</f>
         <v>0</v>
       </c>
-      <c r="I29" s="44"/>
-    </row>
-    <row r="30" customHeight="1" spans="1:9">
+      <c r="I29" s="17"/>
+    </row>
+    <row r="30" ht="21" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="18" t="s">
         <v>119</v>
       </c>
       <c r="B30" s="19">
         <v>24</v>
       </c>
-      <c r="C30" s="15" t="s">
+      <c r="C30" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="D30" s="15" t="s">
+      <c r="D30" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="E30" s="16" t="s">
+      <c r="E30" s="15" t="s">
         <v>81</v>
       </c>
       <c r="F30" s="19">
         <v>56</v>
       </c>
-      <c r="G30" s="15"/>
-      <c r="H30" s="17"/>
-      <c r="I30" s="44"/>
-    </row>
-    <row r="31" customHeight="1" spans="1:9">
+      <c r="G30" s="14"/>
+      <c r="H30" s="16"/>
+      <c r="I30" s="17"/>
+    </row>
+    <row r="31" ht="21" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="18" t="s">
         <v>122</v>
       </c>
       <c r="B31" s="19">
         <v>25</v>
       </c>
-      <c r="C31" s="15" t="s">
+      <c r="C31" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="D31" s="15" t="s">
+      <c r="D31" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="E31" s="16" t="s">
+      <c r="E31" s="15" t="s">
         <v>125</v>
       </c>
       <c r="F31" s="19">
         <v>57</v>
       </c>
-      <c r="G31" s="15"/>
-      <c r="H31" s="17"/>
-      <c r="I31" s="44"/>
-    </row>
-    <row r="32" customHeight="1" spans="1:9">
+      <c r="G31" s="14"/>
+      <c r="H31" s="16"/>
+      <c r="I31" s="17"/>
+    </row>
+    <row r="32" ht="21" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
         <v>126</v>
       </c>
       <c r="B32" s="19">
         <v>26</v>
       </c>
-      <c r="C32" s="15" t="s">
+      <c r="C32" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="D32" s="15" t="s">
+      <c r="D32" s="14" t="s">
         <v>128</v>
       </c>
       <c r="E32" s="20" t="s">
@@ -2836,25 +1876,25 @@
       <c r="F32" s="19">
         <v>58</v>
       </c>
-      <c r="G32" s="15" t="s">
+      <c r="G32" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="H32" s="17" t="s">
+      <c r="H32" s="16" t="s">
         <v>131</v>
       </c>
-      <c r="I32" s="44"/>
-    </row>
-    <row r="33" customHeight="1" spans="1:9">
+      <c r="I32" s="17"/>
+    </row>
+    <row r="33" ht="21" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="18" t="s">
         <v>132</v>
       </c>
       <c r="B33" s="19">
         <v>27</v>
       </c>
-      <c r="C33" s="15" t="s">
+      <c r="C33" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="D33" s="15" t="s">
+      <c r="D33" s="14" t="s">
         <v>134</v>
       </c>
       <c r="E33" s="20" t="s">
@@ -2863,25 +1903,25 @@
       <c r="F33" s="19">
         <v>59</v>
       </c>
-      <c r="G33" s="15" t="s">
+      <c r="G33" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="H33" s="17" t="s">
+      <c r="H33" s="16" t="s">
         <v>137</v>
       </c>
-      <c r="I33" s="44"/>
-    </row>
-    <row r="34" customHeight="1" spans="1:9">
+      <c r="I33" s="17"/>
+    </row>
+    <row r="34" ht="21" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
         <v>138</v>
       </c>
       <c r="B34" s="19">
         <v>28</v>
       </c>
-      <c r="C34" s="15" t="s">
+      <c r="C34" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="D34" s="15" t="s">
+      <c r="D34" s="14" t="s">
         <v>140</v>
       </c>
       <c r="E34" s="20" t="s">
@@ -2890,25 +1930,25 @@
       <c r="F34" s="19">
         <v>60</v>
       </c>
-      <c r="G34" s="15" t="s">
+      <c r="G34" s="14" t="s">
         <v>142</v>
       </c>
-      <c r="H34" s="17" t="s">
+      <c r="H34" s="16" t="s">
         <v>143</v>
       </c>
-      <c r="I34" s="44"/>
-    </row>
-    <row r="35" customHeight="1" spans="1:9">
+      <c r="I34" s="17"/>
+    </row>
+    <row r="35" ht="21" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="18" t="s">
         <v>144</v>
       </c>
       <c r="B35" s="19">
         <v>29</v>
       </c>
-      <c r="C35" s="15" t="s">
+      <c r="C35" s="14" t="s">
         <v>145</v>
       </c>
-      <c r="D35" s="15" t="s">
+      <c r="D35" s="14" t="s">
         <v>146</v>
       </c>
       <c r="E35" s="20" t="s">
@@ -2917,30 +1957,30 @@
       <c r="F35" s="19">
         <v>61</v>
       </c>
-      <c r="G35" s="15" t="s">
+      <c r="G35" s="14" t="s">
         <v>148</v>
       </c>
-      <c r="H35" s="17" t="s">
+      <c r="H35" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="I35" s="44"/>
-    </row>
-    <row r="36" customHeight="1" spans="1:9">
+      <c r="I35" s="17"/>
+    </row>
+    <row r="36" ht="21" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="27"/>
       <c r="B36" s="19">
         <v>30</v>
       </c>
-      <c r="C36" s="15"/>
-      <c r="D36" s="15"/>
+      <c r="C36" s="14"/>
+      <c r="D36" s="14"/>
       <c r="E36" s="28"/>
       <c r="F36" s="19">
         <v>62</v>
       </c>
-      <c r="G36" s="15"/>
-      <c r="H36" s="17"/>
-      <c r="I36" s="44"/>
-    </row>
-    <row r="37" customHeight="1" spans="1:9">
+      <c r="G36" s="14"/>
+      <c r="H36" s="16"/>
+      <c r="I36" s="17"/>
+    </row>
+    <row r="37" ht="21" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="24" t="s">
         <v>150</v>
       </c>
@@ -2969,9 +2009,9 @@
         <f>SUM(H32:H35)</f>
         <v>0</v>
       </c>
-      <c r="I37" s="44"/>
-    </row>
-    <row r="38" ht="33.75" customHeight="1" spans="1:9">
+      <c r="I37" s="17"/>
+    </row>
+    <row r="38" ht="21" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="29" t="s">
         <v>152</v>
       </c>
@@ -3000,9 +2040,9 @@
         <f>H37+H29</f>
         <v>0</v>
       </c>
-      <c r="I38" s="44"/>
-    </row>
-    <row r="39" ht="12.75" customHeight="1" spans="1:9">
+      <c r="I38" s="17"/>
+    </row>
+    <row r="39" ht="21" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="33"/>
       <c r="B39" s="34"/>
       <c r="C39" s="35"/>
@@ -3012,7 +2052,7 @@
       <c r="G39" s="35"/>
       <c r="H39" s="35"/>
     </row>
-    <row r="40" ht="39" customHeight="1" spans="1:9">
+    <row r="40" ht="21" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="36" t="s">
         <v>154</v>
       </c>
@@ -3030,7 +2070,7 @@
       </c>
       <c r="H40" s="1"/>
     </row>
-    <row r="41" customHeight="1" spans="1:9">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -3043,21 +2083,19 @@
   </sheetData>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.393700787401575" right="0.393700787401575" top="0.393700787401575" bottom="0.393700787401575" header="0" footer="0"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="600" verticalDpi="600"/>
-  <headerFooter alignWithMargins="0" scaleWithDoc="0"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="600" verticalDpi="600" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H44"/>
-  <sheetFormatPr defaultColWidth="9.14814814814815" defaultRowHeight="15" outlineLevelCol="7"/>
+  <sheetFormatPr defaultRowHeight="21" outlineLevelRow="0" outlineLevelCol="7" x14ac:dyDescent="0" defaultColWidth="9.14814814814815" customHeight="1"/>
   <cols>
     <col min="1" max="16384" width="9.14814814814815" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3067,35 +2105,35 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
     </row>
-    <row r="2" ht="31.5" spans="1:8">
-      <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="5" t="s">
+    <row r="2" ht="21" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+    </row>
+    <row r="3" ht="21" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="5" t="s">
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="7" t="s">
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="6" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" ht="15.75" spans="1:8">
+    <row r="4" ht="21" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -3105,61 +2143,61 @@
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="8" t="s">
+    <row r="5" ht="21" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="E5" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="10" t="s">
+      <c r="G5" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="12" t="s">
+      <c r="H5" s="11" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="13" t="s">
+    <row r="6" ht="21" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="14"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="16" t="s">
+      <c r="B6" s="13"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="14"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="17"/>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="F6" s="13"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="16"/>
+    </row>
+    <row r="7" ht="21" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="18" t="s">
         <v>13</v>
       </c>
       <c r="B7" s="19">
         <v>1</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="C7" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="15" t="s">
+      <c r="D7" s="14" t="s">
         <v>15</v>
       </c>
       <c r="E7" s="20" t="s">
@@ -3168,24 +2206,24 @@
       <c r="F7" s="19">
         <v>31</v>
       </c>
-      <c r="G7" s="15" t="s">
+      <c r="G7" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="H7" s="17" t="s">
+      <c r="H7" s="16" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" ht="21" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="18" t="s">
         <v>19</v>
       </c>
       <c r="B8" s="19">
         <v>2</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="C8" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="15" t="s">
+      <c r="D8" s="14" t="s">
         <v>21</v>
       </c>
       <c r="E8" s="20" t="s">
@@ -3194,24 +2232,24 @@
       <c r="F8" s="19">
         <v>32</v>
       </c>
-      <c r="G8" s="15" t="s">
+      <c r="G8" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="H8" s="17" t="s">
+      <c r="H8" s="16" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" ht="21" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="18" t="s">
         <v>25</v>
       </c>
       <c r="B9" s="19">
         <v>3</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="C9" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="15" t="s">
+      <c r="D9" s="14" t="s">
         <v>27</v>
       </c>
       <c r="E9" s="20" t="s">
@@ -3220,24 +2258,24 @@
       <c r="F9" s="19">
         <v>33</v>
       </c>
-      <c r="G9" s="15" t="s">
+      <c r="G9" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="H9" s="17" t="s">
+      <c r="H9" s="16" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" ht="21" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="18" t="s">
         <v>31</v>
       </c>
       <c r="B10" s="19">
         <v>4</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="C10" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="D10" s="15" t="s">
+      <c r="D10" s="14" t="s">
         <v>33</v>
       </c>
       <c r="E10" s="20" t="s">
@@ -3246,24 +2284,24 @@
       <c r="F10" s="19">
         <v>34</v>
       </c>
-      <c r="G10" s="15" t="s">
+      <c r="G10" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="H10" s="17" t="s">
+      <c r="H10" s="16" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" ht="21" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="18" t="s">
         <v>37</v>
       </c>
       <c r="B11" s="19">
         <v>5</v>
       </c>
-      <c r="C11" s="15" t="s">
+      <c r="C11" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="D11" s="15" t="s">
+      <c r="D11" s="14" t="s">
         <v>39</v>
       </c>
       <c r="E11" s="20" t="s">
@@ -3272,24 +2310,24 @@
       <c r="F11" s="19">
         <v>35</v>
       </c>
-      <c r="G11" s="15" t="s">
+      <c r="G11" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="H11" s="17" t="s">
+      <c r="H11" s="16" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" ht="21" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="18" t="s">
         <v>43</v>
       </c>
       <c r="B12" s="19">
         <v>6</v>
       </c>
-      <c r="C12" s="15" t="s">
+      <c r="C12" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="D12" s="15" t="s">
+      <c r="D12" s="14" t="s">
         <v>45</v>
       </c>
       <c r="E12" s="20" t="s">
@@ -3298,24 +2336,24 @@
       <c r="F12" s="19">
         <v>36</v>
       </c>
-      <c r="G12" s="15" t="s">
+      <c r="G12" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="H12" s="17" t="s">
+      <c r="H12" s="16" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" ht="21" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
         <v>49</v>
       </c>
       <c r="B13" s="19">
         <v>7</v>
       </c>
-      <c r="C13" s="15" t="s">
+      <c r="C13" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="D13" s="14" t="s">
         <v>51</v>
       </c>
       <c r="E13" s="20" t="s">
@@ -3324,24 +2362,24 @@
       <c r="F13" s="19">
         <v>37</v>
       </c>
-      <c r="G13" s="15" t="s">
+      <c r="G13" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="H13" s="17" t="s">
+      <c r="H13" s="16" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" ht="21" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="18" t="s">
         <v>55</v>
       </c>
       <c r="B14" s="19">
         <v>8</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="C14" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="D14" s="15" t="s">
+      <c r="D14" s="14" t="s">
         <v>57</v>
       </c>
       <c r="E14" s="20" t="s">
@@ -3350,24 +2388,24 @@
       <c r="F14" s="19">
         <v>38</v>
       </c>
-      <c r="G14" s="15" t="s">
+      <c r="G14" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="H14" s="17" t="s">
+      <c r="H14" s="16" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" ht="21" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="s">
         <v>61</v>
       </c>
       <c r="B15" s="19">
         <v>9</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="C15" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="D15" s="15" t="s">
+      <c r="D15" s="14" t="s">
         <v>63</v>
       </c>
       <c r="E15" s="20" t="s">
@@ -3376,24 +2414,24 @@
       <c r="F15" s="19">
         <v>39</v>
       </c>
-      <c r="G15" s="15" t="s">
+      <c r="G15" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="H15" s="17" t="s">
+      <c r="H15" s="16" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" ht="21" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="18" t="s">
         <v>67</v>
       </c>
       <c r="B16" s="19">
         <v>10</v>
       </c>
-      <c r="C16" s="15" t="s">
+      <c r="C16" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="D16" s="15" t="s">
+      <c r="D16" s="14" t="s">
         <v>69</v>
       </c>
       <c r="E16" s="20" t="s">
@@ -3402,38 +2440,38 @@
       <c r="F16" s="19">
         <v>40</v>
       </c>
-      <c r="G16" s="15"/>
-      <c r="H16" s="17"/>
-    </row>
-    <row r="17" spans="1:8">
+      <c r="G16" s="14"/>
+      <c r="H16" s="16"/>
+    </row>
+    <row r="17" ht="21" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="18" t="s">
         <v>71</v>
       </c>
       <c r="B17" s="19">
         <v>11</v>
       </c>
-      <c r="C17" s="15" t="s">
+      <c r="C17" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="D17" s="15" t="s">
+      <c r="D17" s="14" t="s">
         <v>73</v>
       </c>
       <c r="E17" s="21"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="15"/>
-      <c r="H17" s="17"/>
-    </row>
-    <row r="18" spans="1:8">
+      <c r="F17" s="13"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="16"/>
+    </row>
+    <row r="18" ht="21" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="18" t="s">
         <v>74</v>
       </c>
       <c r="B18" s="19">
         <v>12</v>
       </c>
-      <c r="C18" s="15" t="s">
+      <c r="C18" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="D18" s="15" t="s">
+      <c r="D18" s="14" t="s">
         <v>76</v>
       </c>
       <c r="E18" s="22" t="s">
@@ -3451,39 +2489,39 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" ht="21" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="18" t="s">
         <v>78</v>
       </c>
       <c r="B19" s="19">
         <v>13</v>
       </c>
-      <c r="C19" s="15" t="s">
+      <c r="C19" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="D19" s="15" t="s">
+      <c r="D19" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="E19" s="16" t="s">
+      <c r="E19" s="15" t="s">
         <v>81</v>
       </c>
       <c r="F19" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="G19" s="15"/>
-      <c r="H19" s="17"/>
-    </row>
-    <row r="20" spans="1:8">
+      <c r="G19" s="14"/>
+      <c r="H19" s="16"/>
+    </row>
+    <row r="20" ht="21" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="18" t="s">
         <v>82</v>
       </c>
       <c r="B20" s="19">
         <v>14</v>
       </c>
-      <c r="C20" s="15" t="s">
+      <c r="C20" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="D20" s="15" t="s">
+      <c r="D20" s="14" t="s">
         <v>84</v>
       </c>
       <c r="E20" s="20" t="s">
@@ -3492,14 +2530,14 @@
       <c r="F20" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="G20" s="15" t="s">
+      <c r="G20" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="H20" s="17" t="s">
+      <c r="H20" s="16" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" ht="21" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="24" t="s">
         <v>85</v>
       </c>
@@ -3520,42 +2558,42 @@
       <c r="F21" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="G21" s="15" t="s">
+      <c r="G21" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="H21" s="17" t="s">
+      <c r="H21" s="16" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
-      <c r="A22" s="13" t="s">
+    <row r="22" ht="21" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="12" t="s">
         <v>86</v>
       </c>
       <c r="B22" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="C22" s="15"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="16" t="s">
+      <c r="C22" s="14"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="15" t="s">
         <v>87</v>
       </c>
       <c r="F22" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="G22" s="15"/>
-      <c r="H22" s="17"/>
-    </row>
-    <row r="23" spans="1:8">
+      <c r="G22" s="14"/>
+      <c r="H22" s="16"/>
+    </row>
+    <row r="23" ht="21" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="18" t="s">
         <v>88</v>
       </c>
       <c r="B23" s="19">
         <v>16</v>
       </c>
-      <c r="C23" s="15" t="s">
+      <c r="C23" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="D23" s="15" t="s">
+      <c r="D23" s="14" t="s">
         <v>90</v>
       </c>
       <c r="E23" s="20" t="s">
@@ -3564,24 +2602,24 @@
       <c r="F23" s="19">
         <v>42</v>
       </c>
-      <c r="G23" s="15" t="s">
+      <c r="G23" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="H23" s="17" t="s">
+      <c r="H23" s="16" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" ht="21" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="18" t="s">
         <v>94</v>
       </c>
       <c r="B24" s="19">
         <v>17</v>
       </c>
-      <c r="C24" s="15" t="s">
+      <c r="C24" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="D24" s="15" t="s">
+      <c r="D24" s="14" t="s">
         <v>96</v>
       </c>
       <c r="E24" s="20" t="s">
@@ -3590,24 +2628,24 @@
       <c r="F24" s="19">
         <v>43</v>
       </c>
-      <c r="G24" s="15" t="s">
+      <c r="G24" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="H24" s="17" t="s">
+      <c r="H24" s="16" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" ht="21" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="18" t="s">
         <v>100</v>
       </c>
       <c r="B25" s="19">
         <v>18</v>
       </c>
-      <c r="C25" s="15" t="s">
+      <c r="C25" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="D25" s="15" t="s">
+      <c r="D25" s="14" t="s">
         <v>102</v>
       </c>
       <c r="E25" s="20" t="s">
@@ -3616,24 +2654,24 @@
       <c r="F25" s="19">
         <v>44</v>
       </c>
-      <c r="G25" s="15" t="s">
+      <c r="G25" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="H25" s="17" t="s">
+      <c r="H25" s="16" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" ht="21" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="18" t="s">
         <v>106</v>
       </c>
       <c r="B26" s="19">
         <v>19</v>
       </c>
-      <c r="C26" s="15" t="s">
+      <c r="C26" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="D26" s="15" t="s">
+      <c r="D26" s="14" t="s">
         <v>108</v>
       </c>
       <c r="E26" s="20" t="s">
@@ -3642,40 +2680,40 @@
       <c r="F26" s="19">
         <v>45</v>
       </c>
-      <c r="G26" s="15"/>
-      <c r="H26" s="17"/>
-    </row>
-    <row r="27" spans="1:8">
+      <c r="G26" s="14"/>
+      <c r="H26" s="16"/>
+    </row>
+    <row r="27" ht="21" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="18" t="s">
         <v>110</v>
       </c>
       <c r="B27" s="19">
         <v>20</v>
       </c>
-      <c r="C27" s="15" t="e">
+      <c r="C27" s="14" t="e">
         <f>C25-C26</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D27" s="15" t="e">
+      <c r="D27" s="14" t="e">
         <f>D25-D26</f>
         <v>#VALUE!</v>
       </c>
       <c r="E27" s="21"/>
-      <c r="F27" s="14"/>
+      <c r="F27" s="13"/>
       <c r="G27" s="25"/>
       <c r="H27" s="26"/>
     </row>
-    <row r="28" spans="1:8">
+    <row r="28" ht="21" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="18" t="s">
         <v>111</v>
       </c>
       <c r="B28" s="19">
         <v>21</v>
       </c>
-      <c r="C28" s="15" t="s">
+      <c r="C28" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="D28" s="15" t="s">
+      <c r="D28" s="14" t="s">
         <v>113</v>
       </c>
       <c r="E28" s="22" t="s">
@@ -3693,17 +2731,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" ht="21" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="18" t="s">
         <v>115</v>
       </c>
       <c r="B29" s="19">
         <v>22</v>
       </c>
-      <c r="C29" s="15" t="s">
+      <c r="C29" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="D29" s="15" t="s">
+      <c r="D29" s="14" t="s">
         <v>117</v>
       </c>
       <c r="E29" s="22" t="s">
@@ -3721,61 +2759,61 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" ht="21" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="18" t="s">
         <v>119</v>
       </c>
       <c r="B30" s="19">
         <v>23</v>
       </c>
-      <c r="C30" s="15" t="s">
+      <c r="C30" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="D30" s="15" t="s">
+      <c r="D30" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="E30" s="16" t="s">
+      <c r="E30" s="15" t="s">
         <v>81</v>
       </c>
       <c r="F30" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="G30" s="15"/>
-      <c r="H30" s="17"/>
-    </row>
-    <row r="31" spans="1:8">
+      <c r="G30" s="14"/>
+      <c r="H30" s="16"/>
+    </row>
+    <row r="31" ht="21" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="18" t="s">
         <v>122</v>
       </c>
       <c r="B31" s="19">
         <v>24</v>
       </c>
-      <c r="C31" s="15" t="s">
+      <c r="C31" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="D31" s="15" t="s">
+      <c r="D31" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="E31" s="16" t="s">
+      <c r="E31" s="15" t="s">
         <v>125</v>
       </c>
       <c r="F31" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="G31" s="15"/>
-      <c r="H31" s="17"/>
-    </row>
-    <row r="32" spans="1:8">
+      <c r="G31" s="14"/>
+      <c r="H31" s="16"/>
+    </row>
+    <row r="32" ht="21" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
         <v>126</v>
       </c>
       <c r="B32" s="19">
         <v>25</v>
       </c>
-      <c r="C32" s="15" t="s">
+      <c r="C32" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="D32" s="15" t="s">
+      <c r="D32" s="14" t="s">
         <v>128</v>
       </c>
       <c r="E32" s="20" t="s">
@@ -3784,24 +2822,24 @@
       <c r="F32" s="19">
         <v>48</v>
       </c>
-      <c r="G32" s="15" t="s">
+      <c r="G32" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="H32" s="17" t="s">
+      <c r="H32" s="16" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="33" spans="1:8">
+    <row r="33" ht="21" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="18" t="s">
         <v>132</v>
       </c>
       <c r="B33" s="19">
         <v>26</v>
       </c>
-      <c r="C33" s="15" t="s">
+      <c r="C33" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="D33" s="15" t="s">
+      <c r="D33" s="14" t="s">
         <v>134</v>
       </c>
       <c r="E33" s="20" t="s">
@@ -3810,24 +2848,24 @@
       <c r="F33" s="19">
         <v>49</v>
       </c>
-      <c r="G33" s="15" t="s">
+      <c r="G33" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="H33" s="17" t="s">
+      <c r="H33" s="16" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="34" spans="1:8">
+    <row r="34" ht="21" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
         <v>138</v>
       </c>
       <c r="B34" s="19">
         <v>27</v>
       </c>
-      <c r="C34" s="15" t="s">
+      <c r="C34" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="D34" s="15" t="s">
+      <c r="D34" s="14" t="s">
         <v>140</v>
       </c>
       <c r="E34" s="20" t="s">
@@ -3836,24 +2874,24 @@
       <c r="F34" s="19">
         <v>50</v>
       </c>
-      <c r="G34" s="15" t="s">
+      <c r="G34" s="14" t="s">
         <v>142</v>
       </c>
-      <c r="H34" s="17" t="s">
+      <c r="H34" s="16" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="35" spans="1:8">
+    <row r="35" ht="21" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="18" t="s">
         <v>144</v>
       </c>
       <c r="B35" s="19">
         <v>28</v>
       </c>
-      <c r="C35" s="15" t="s">
+      <c r="C35" s="14" t="s">
         <v>145</v>
       </c>
-      <c r="D35" s="15" t="s">
+      <c r="D35" s="14" t="s">
         <v>146</v>
       </c>
       <c r="E35" s="20" t="s">
@@ -3862,28 +2900,28 @@
       <c r="F35" s="19">
         <v>51</v>
       </c>
-      <c r="G35" s="15" t="s">
+      <c r="G35" s="14" t="s">
         <v>148</v>
       </c>
-      <c r="H35" s="17" t="s">
+      <c r="H35" s="16" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="36" spans="1:8">
+    <row r="36" ht="21" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="27"/>
       <c r="B36" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="C36" s="15"/>
-      <c r="D36" s="15"/>
+      <c r="C36" s="14"/>
+      <c r="D36" s="14"/>
       <c r="E36" s="28"/>
       <c r="F36" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="G36" s="15"/>
-      <c r="H36" s="17"/>
-    </row>
-    <row r="37" spans="1:8">
+      <c r="G36" s="14"/>
+      <c r="H36" s="16"/>
+    </row>
+    <row r="37" ht="21" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="24" t="s">
         <v>150</v>
       </c>
@@ -3913,7 +2951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" ht="72" spans="1:8">
+    <row r="38" ht="21" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="29" t="s">
         <v>152</v>
       </c>
@@ -3944,7 +2982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:8">
+    <row r="39" ht="21" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="33"/>
       <c r="B39" s="34"/>
       <c r="C39" s="35"/>
@@ -3954,7 +2992,7 @@
       <c r="G39" s="35"/>
       <c r="H39" s="35"/>
     </row>
-    <row r="40" spans="1:8">
+    <row r="40" ht="21" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="36" t="s">
         <v>154</v>
       </c>
@@ -3972,7 +3010,7 @@
       </c>
       <c r="H40" s="1"/>
     </row>
-    <row r="41" spans="1:8">
+    <row r="41" ht="21" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -3982,15 +3020,15 @@
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
     </row>
-    <row r="42" ht="72" spans="1:8">
+    <row r="42" ht="21" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="29" t="s">
         <v>152</v>
       </c>
-      <c r="B42" s="38">
+      <c r="B42" s="37">
         <f>B41+1</f>
         <v>1</v>
       </c>
-      <c r="C42" s="39" t="e">
+      <c r="C42" s="38" t="e">
         <f>C21+C41</f>
         <v>#VALUE!</v>
       </c>
@@ -4001,50 +3039,50 @@
       <c r="E42" s="32" t="s">
         <v>153</v>
       </c>
-      <c r="F42" s="40">
+      <c r="F42" s="39">
         <f>F41+1</f>
         <v>1</v>
       </c>
-      <c r="G42" s="39">
+      <c r="G42" s="38">
         <f>G31+G41</f>
         <v>0</v>
       </c>
-      <c r="H42" s="41">
+      <c r="H42" s="40">
         <f>H31+H41</f>
         <v>0</v>
       </c>
     </row>
-    <row r="43" ht="15.75" spans="1:8">
+    <row r="43" ht="21" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="33"/>
-      <c r="B43" s="42"/>
-      <c r="C43" s="43"/>
-      <c r="D43" s="43"/>
+      <c r="B43" s="41"/>
+      <c r="C43" s="42"/>
+      <c r="D43" s="42"/>
       <c r="E43" s="33"/>
-      <c r="F43" s="42"/>
-      <c r="G43" s="43"/>
-      <c r="H43" s="43"/>
-    </row>
-    <row r="44" ht="15.75" spans="1:8">
-      <c r="A44" s="37" t="s">
+      <c r="F43" s="41"/>
+      <c r="G43" s="42"/>
+      <c r="H43" s="42"/>
+    </row>
+    <row r="44" ht="21" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="43" t="s">
         <v>158</v>
       </c>
-      <c r="B44" s="37"/>
-      <c r="C44" s="37" t="s">
+      <c r="B44" s="43"/>
+      <c r="C44" s="43" t="s">
         <v>159</v>
       </c>
-      <c r="D44" s="37"/>
-      <c r="E44" s="37" t="s">
+      <c r="D44" s="43"/>
+      <c r="E44" s="43" t="s">
         <v>160</v>
       </c>
-      <c r="F44" s="37"/>
-      <c r="G44" s="37" t="s">
+      <c r="F44" s="43"/>
+      <c r="G44" s="43" t="s">
         <v>161</v>
       </c>
     </row>
   </sheetData>
   <printOptions gridLines="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter alignWithMargins="0" scaleWithDoc="0">
+  <headerFooter>
     <oddHeader>&amp;C&amp;A</oddHeader>
     <oddFooter>&amp;CPage &amp;P</oddFooter>
   </headerFooter>
@@ -4052,15 +3090,14 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:U42"/>
-  <sheetFormatPr defaultColWidth="9.14814814814815" defaultRowHeight="17" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="21" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="9.14814814814815" customHeight="1"/>
   <cols>
     <col min="1" max="16384" width="9.14814814814815" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:21">
+    <row r="1" ht="28" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4069,74 +3106,74 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="2"/>
-      <c r="S1" s="2"/>
-      <c r="T1" s="2"/>
-      <c r="U1" s="2"/>
-    </row>
-    <row r="2" customHeight="1" spans="1:21">
-      <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2"/>
-      <c r="P2" s="2"/>
-      <c r="Q2" s="2"/>
-      <c r="R2" s="2"/>
-      <c r="S2" s="2"/>
-      <c r="T2" s="2"/>
-      <c r="U2" s="2"/>
-    </row>
-    <row r="3" customHeight="1" spans="1:21">
-      <c r="A3" s="5" t="s">
+      <c r="I1" s="44"/>
+      <c r="J1" s="44"/>
+      <c r="K1" s="44"/>
+      <c r="L1" s="44"/>
+      <c r="M1" s="44"/>
+      <c r="N1" s="44"/>
+      <c r="O1" s="44"/>
+      <c r="P1" s="44"/>
+      <c r="Q1" s="44"/>
+      <c r="R1" s="44"/>
+      <c r="S1" s="44"/>
+      <c r="T1" s="44"/>
+      <c r="U1" s="44"/>
+    </row>
+    <row r="2" ht="21" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="44"/>
+      <c r="J2" s="44"/>
+      <c r="K2" s="44"/>
+      <c r="L2" s="44"/>
+      <c r="M2" s="44"/>
+      <c r="N2" s="44"/>
+      <c r="O2" s="44"/>
+      <c r="P2" s="44"/>
+      <c r="Q2" s="44"/>
+      <c r="R2" s="44"/>
+      <c r="S2" s="44"/>
+      <c r="T2" s="44"/>
+      <c r="U2" s="44"/>
+    </row>
+    <row r="3" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="5" t="s">
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="7" t="s">
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2"/>
-      <c r="O3" s="2"/>
-      <c r="P3" s="2"/>
-      <c r="Q3" s="2"/>
-      <c r="R3" s="2"/>
-      <c r="S3" s="2"/>
-      <c r="T3" s="2"/>
-    </row>
-    <row r="4" customHeight="1" spans="1:21">
+      <c r="I3" s="44"/>
+      <c r="J3" s="44"/>
+      <c r="K3" s="44"/>
+      <c r="L3" s="44"/>
+      <c r="M3" s="44"/>
+      <c r="N3" s="44"/>
+      <c r="O3" s="44"/>
+      <c r="P3" s="44"/>
+      <c r="Q3" s="44"/>
+      <c r="R3" s="44"/>
+      <c r="S3" s="44"/>
+      <c r="T3" s="44"/>
+    </row>
+    <row r="4" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -4146,98 +3183,98 @@
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2"/>
-      <c r="O4" s="2"/>
-      <c r="P4" s="2"/>
-      <c r="Q4" s="2"/>
-      <c r="R4" s="2"/>
-      <c r="S4" s="2"/>
-      <c r="T4" s="2"/>
-    </row>
-    <row r="5" customHeight="1" spans="1:21">
-      <c r="A5" s="8" t="s">
+      <c r="I4" s="44"/>
+      <c r="J4" s="44"/>
+      <c r="K4" s="44"/>
+      <c r="L4" s="44"/>
+      <c r="M4" s="44"/>
+      <c r="N4" s="44"/>
+      <c r="O4" s="44"/>
+      <c r="P4" s="44"/>
+      <c r="Q4" s="44"/>
+      <c r="R4" s="44"/>
+      <c r="S4" s="44"/>
+      <c r="T4" s="44"/>
+    </row>
+    <row r="5" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="E5" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="10" t="s">
+      <c r="G5" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="12" t="s">
+      <c r="H5" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2"/>
-      <c r="O5" s="2"/>
-      <c r="P5" s="2"/>
-      <c r="Q5" s="2"/>
-      <c r="R5" s="2"/>
-      <c r="S5" s="2"/>
-      <c r="T5" s="2"/>
-    </row>
-    <row r="6" customHeight="1" spans="1:21">
-      <c r="A6" s="13" t="s">
+      <c r="I5" s="44"/>
+      <c r="J5" s="44"/>
+      <c r="K5" s="44"/>
+      <c r="L5" s="44"/>
+      <c r="M5" s="44"/>
+      <c r="N5" s="44"/>
+      <c r="O5" s="44"/>
+      <c r="P5" s="44"/>
+      <c r="Q5" s="44"/>
+      <c r="R5" s="44"/>
+      <c r="S5" s="44"/>
+      <c r="T5" s="44"/>
+    </row>
+    <row r="6" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A6" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="14"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="16" t="s">
+      <c r="B6" s="13"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="14"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="17"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2"/>
-      <c r="O6" s="2"/>
-      <c r="P6" s="2"/>
-      <c r="Q6" s="2"/>
-      <c r="R6" s="2"/>
-      <c r="S6" s="2"/>
-      <c r="T6" s="2"/>
-    </row>
-    <row r="7" customHeight="1" spans="1:21">
+      <c r="F6" s="13"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="44"/>
+      <c r="J6" s="44"/>
+      <c r="K6" s="44"/>
+      <c r="L6" s="44"/>
+      <c r="M6" s="44"/>
+      <c r="N6" s="44"/>
+      <c r="O6" s="44"/>
+      <c r="P6" s="44"/>
+      <c r="Q6" s="44"/>
+      <c r="R6" s="44"/>
+      <c r="S6" s="44"/>
+      <c r="T6" s="44"/>
+    </row>
+    <row r="7" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" s="18" t="s">
         <v>13</v>
       </c>
       <c r="B7" s="19">
         <v>1</v>
       </c>
-      <c r="C7" s="15">
+      <c r="C7" s="14">
         <f t="shared" ref="C7:C19" si="0">0</f>
         <v>0</v>
       </c>
-      <c r="D7" s="15">
+      <c r="D7" s="14">
         <f t="shared" ref="D7:D19" si="1">0</f>
         <v>0</v>
       </c>
@@ -4247,39 +3284,39 @@
       <c r="F7" s="19">
         <v>31</v>
       </c>
-      <c r="G7" s="15">
+      <c r="G7" s="14">
         <f t="shared" ref="G7:G15" si="2">0</f>
         <v>0</v>
       </c>
-      <c r="H7" s="17">
+      <c r="H7" s="16">
         <f t="shared" ref="H7:H15" si="3">0</f>
         <v>0</v>
       </c>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2"/>
-      <c r="O7" s="2"/>
-      <c r="P7" s="2"/>
-      <c r="Q7" s="2"/>
-      <c r="R7" s="2"/>
-      <c r="S7" s="2"/>
-      <c r="T7" s="2"/>
-    </row>
-    <row r="8" customHeight="1" spans="1:21">
+      <c r="I7" s="44"/>
+      <c r="J7" s="44"/>
+      <c r="K7" s="44"/>
+      <c r="L7" s="44"/>
+      <c r="M7" s="44"/>
+      <c r="N7" s="44"/>
+      <c r="O7" s="44"/>
+      <c r="P7" s="44"/>
+      <c r="Q7" s="44"/>
+      <c r="R7" s="44"/>
+      <c r="S7" s="44"/>
+      <c r="T7" s="44"/>
+    </row>
+    <row r="8" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" s="18" t="s">
         <v>19</v>
       </c>
       <c r="B8" s="19">
         <v>2</v>
       </c>
-      <c r="C8" s="15">
+      <c r="C8" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D8" s="15">
+      <c r="D8" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4289,39 +3326,39 @@
       <c r="F8" s="19">
         <v>32</v>
       </c>
-      <c r="G8" s="15">
+      <c r="G8" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H8" s="17">
+      <c r="H8" s="16">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2"/>
-      <c r="O8" s="2"/>
-      <c r="P8" s="2"/>
-      <c r="Q8" s="2"/>
-      <c r="R8" s="2"/>
-      <c r="S8" s="2"/>
-      <c r="T8" s="2"/>
-    </row>
-    <row r="9" customHeight="1" spans="1:21">
+      <c r="I8" s="44"/>
+      <c r="J8" s="44"/>
+      <c r="K8" s="44"/>
+      <c r="L8" s="44"/>
+      <c r="M8" s="44"/>
+      <c r="N8" s="44"/>
+      <c r="O8" s="44"/>
+      <c r="P8" s="44"/>
+      <c r="Q8" s="44"/>
+      <c r="R8" s="44"/>
+      <c r="S8" s="44"/>
+      <c r="T8" s="44"/>
+    </row>
+    <row r="9" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" s="18" t="s">
         <v>25</v>
       </c>
       <c r="B9" s="19">
         <v>3</v>
       </c>
-      <c r="C9" s="15">
+      <c r="C9" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D9" s="15">
+      <c r="D9" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4331,39 +3368,39 @@
       <c r="F9" s="19">
         <v>33</v>
       </c>
-      <c r="G9" s="15">
+      <c r="G9" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H9" s="17">
+      <c r="H9" s="16">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
-      <c r="M9" s="2"/>
-      <c r="N9" s="2"/>
-      <c r="O9" s="2"/>
-      <c r="P9" s="2"/>
-      <c r="Q9" s="2"/>
-      <c r="R9" s="2"/>
-      <c r="S9" s="2"/>
-      <c r="T9" s="2"/>
-    </row>
-    <row r="10" customHeight="1" spans="1:21">
+      <c r="I9" s="44"/>
+      <c r="J9" s="44"/>
+      <c r="K9" s="44"/>
+      <c r="L9" s="44"/>
+      <c r="M9" s="44"/>
+      <c r="N9" s="44"/>
+      <c r="O9" s="44"/>
+      <c r="P9" s="44"/>
+      <c r="Q9" s="44"/>
+      <c r="R9" s="44"/>
+      <c r="S9" s="44"/>
+      <c r="T9" s="44"/>
+    </row>
+    <row r="10" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" s="18" t="s">
         <v>164</v>
       </c>
       <c r="B10" s="19">
         <v>4</v>
       </c>
-      <c r="C10" s="15">
+      <c r="C10" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D10" s="15">
+      <c r="D10" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4373,39 +3410,39 @@
       <c r="F10" s="19">
         <v>34</v>
       </c>
-      <c r="G10" s="15">
+      <c r="G10" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H10" s="17">
+      <c r="H10" s="16">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
-      <c r="N10" s="2"/>
-      <c r="O10" s="2"/>
-      <c r="P10" s="2"/>
-      <c r="Q10" s="2"/>
-      <c r="R10" s="2"/>
-      <c r="S10" s="2"/>
-      <c r="T10" s="2"/>
-    </row>
-    <row r="11" customHeight="1" spans="1:21">
+      <c r="I10" s="44"/>
+      <c r="J10" s="44"/>
+      <c r="K10" s="44"/>
+      <c r="L10" s="44"/>
+      <c r="M10" s="44"/>
+      <c r="N10" s="44"/>
+      <c r="O10" s="44"/>
+      <c r="P10" s="44"/>
+      <c r="Q10" s="44"/>
+      <c r="R10" s="44"/>
+      <c r="S10" s="44"/>
+      <c r="T10" s="44"/>
+    </row>
+    <row r="11" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" s="18" t="s">
         <v>37</v>
       </c>
       <c r="B11" s="19">
         <v>5</v>
       </c>
-      <c r="C11" s="15">
+      <c r="C11" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D11" s="15">
+      <c r="D11" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4415,39 +3452,39 @@
       <c r="F11" s="19">
         <v>35</v>
       </c>
-      <c r="G11" s="15">
+      <c r="G11" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H11" s="17">
+      <c r="H11" s="16">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
-      <c r="P11" s="2"/>
-      <c r="Q11" s="2"/>
-      <c r="R11" s="2"/>
-      <c r="S11" s="2"/>
-      <c r="T11" s="2"/>
-    </row>
-    <row r="12" customHeight="1" spans="1:21">
+      <c r="I11" s="44"/>
+      <c r="J11" s="44"/>
+      <c r="K11" s="44"/>
+      <c r="L11" s="44"/>
+      <c r="M11" s="44"/>
+      <c r="N11" s="44"/>
+      <c r="O11" s="44"/>
+      <c r="P11" s="44"/>
+      <c r="Q11" s="44"/>
+      <c r="R11" s="44"/>
+      <c r="S11" s="44"/>
+      <c r="T11" s="44"/>
+    </row>
+    <row r="12" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" s="18" t="s">
         <v>43</v>
       </c>
       <c r="B12" s="19">
         <v>6</v>
       </c>
-      <c r="C12" s="15">
+      <c r="C12" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D12" s="15">
+      <c r="D12" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4457,39 +3494,39 @@
       <c r="F12" s="19">
         <v>36</v>
       </c>
-      <c r="G12" s="15">
+      <c r="G12" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H12" s="17">
+      <c r="H12" s="16">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
-      <c r="P12" s="2"/>
-      <c r="Q12" s="2"/>
-      <c r="R12" s="2"/>
-      <c r="S12" s="2"/>
-      <c r="T12" s="2"/>
-    </row>
-    <row r="13" customHeight="1" spans="1:21">
+      <c r="I12" s="44"/>
+      <c r="J12" s="44"/>
+      <c r="K12" s="44"/>
+      <c r="L12" s="44"/>
+      <c r="M12" s="44"/>
+      <c r="N12" s="44"/>
+      <c r="O12" s="44"/>
+      <c r="P12" s="44"/>
+      <c r="Q12" s="44"/>
+      <c r="R12" s="44"/>
+      <c r="S12" s="44"/>
+      <c r="T12" s="44"/>
+    </row>
+    <row r="13" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
         <v>49</v>
       </c>
       <c r="B13" s="19">
         <v>7</v>
       </c>
-      <c r="C13" s="15">
+      <c r="C13" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D13" s="15">
+      <c r="D13" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4499,39 +3536,39 @@
       <c r="F13" s="19">
         <v>37</v>
       </c>
-      <c r="G13" s="15">
+      <c r="G13" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H13" s="17">
+      <c r="H13" s="16">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2"/>
-      <c r="O13" s="2"/>
-      <c r="P13" s="2"/>
-      <c r="Q13" s="2"/>
-      <c r="R13" s="2"/>
-      <c r="S13" s="2"/>
-      <c r="T13" s="2"/>
-    </row>
-    <row r="14" customHeight="1" spans="1:21">
+      <c r="I13" s="44"/>
+      <c r="J13" s="44"/>
+      <c r="K13" s="44"/>
+      <c r="L13" s="44"/>
+      <c r="M13" s="44"/>
+      <c r="N13" s="44"/>
+      <c r="O13" s="44"/>
+      <c r="P13" s="44"/>
+      <c r="Q13" s="44"/>
+      <c r="R13" s="44"/>
+      <c r="S13" s="44"/>
+      <c r="T13" s="44"/>
+    </row>
+    <row r="14" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" s="18" t="s">
         <v>55</v>
       </c>
       <c r="B14" s="19">
         <v>8</v>
       </c>
-      <c r="C14" s="15">
+      <c r="C14" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D14" s="15">
+      <c r="D14" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4541,39 +3578,39 @@
       <c r="F14" s="19">
         <v>38</v>
       </c>
-      <c r="G14" s="15">
+      <c r="G14" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H14" s="17">
+      <c r="H14" s="16">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
-      <c r="N14" s="2"/>
-      <c r="O14" s="2"/>
-      <c r="P14" s="2"/>
-      <c r="Q14" s="2"/>
-      <c r="R14" s="2"/>
-      <c r="S14" s="2"/>
-      <c r="T14" s="2"/>
-    </row>
-    <row r="15" customHeight="1" spans="1:21">
+      <c r="I14" s="44"/>
+      <c r="J14" s="44"/>
+      <c r="K14" s="44"/>
+      <c r="L14" s="44"/>
+      <c r="M14" s="44"/>
+      <c r="N14" s="44"/>
+      <c r="O14" s="44"/>
+      <c r="P14" s="44"/>
+      <c r="Q14" s="44"/>
+      <c r="R14" s="44"/>
+      <c r="S14" s="44"/>
+      <c r="T14" s="44"/>
+    </row>
+    <row r="15" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="s">
         <v>61</v>
       </c>
       <c r="B15" s="19">
         <v>9</v>
       </c>
-      <c r="C15" s="15">
+      <c r="C15" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D15" s="15">
+      <c r="D15" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4583,39 +3620,39 @@
       <c r="F15" s="19">
         <v>39</v>
       </c>
-      <c r="G15" s="15">
+      <c r="G15" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H15" s="17">
+      <c r="H15" s="16">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
-      <c r="L15" s="2"/>
-      <c r="M15" s="2"/>
-      <c r="N15" s="2"/>
-      <c r="O15" s="2"/>
-      <c r="P15" s="2"/>
-      <c r="Q15" s="2"/>
-      <c r="R15" s="2"/>
-      <c r="S15" s="2"/>
-      <c r="T15" s="2"/>
-    </row>
-    <row r="16" customHeight="1" spans="1:21">
+      <c r="I15" s="44"/>
+      <c r="J15" s="44"/>
+      <c r="K15" s="44"/>
+      <c r="L15" s="44"/>
+      <c r="M15" s="44"/>
+      <c r="N15" s="44"/>
+      <c r="O15" s="44"/>
+      <c r="P15" s="44"/>
+      <c r="Q15" s="44"/>
+      <c r="R15" s="44"/>
+      <c r="S15" s="44"/>
+      <c r="T15" s="44"/>
+    </row>
+    <row r="16" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" s="18" t="s">
         <v>67</v>
       </c>
       <c r="B16" s="19">
         <v>10</v>
       </c>
-      <c r="C16" s="15">
+      <c r="C16" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D16" s="15">
+      <c r="D16" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4625,65 +3662,65 @@
       <c r="F16" s="19">
         <v>40</v>
       </c>
-      <c r="G16" s="15"/>
-      <c r="H16" s="17"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
-      <c r="L16" s="2"/>
-      <c r="M16" s="2"/>
-      <c r="N16" s="2"/>
-      <c r="O16" s="2"/>
-      <c r="P16" s="2"/>
-      <c r="Q16" s="2"/>
-      <c r="R16" s="2"/>
-      <c r="S16" s="2"/>
-      <c r="T16" s="2"/>
-    </row>
-    <row r="17" customHeight="1" spans="1:20">
+      <c r="G16" s="14"/>
+      <c r="H16" s="16"/>
+      <c r="I16" s="44"/>
+      <c r="J16" s="44"/>
+      <c r="K16" s="44"/>
+      <c r="L16" s="44"/>
+      <c r="M16" s="44"/>
+      <c r="N16" s="44"/>
+      <c r="O16" s="44"/>
+      <c r="P16" s="44"/>
+      <c r="Q16" s="44"/>
+      <c r="R16" s="44"/>
+      <c r="S16" s="44"/>
+      <c r="T16" s="44"/>
+    </row>
+    <row r="17" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17" s="18" t="s">
         <v>71</v>
       </c>
       <c r="B17" s="19">
         <v>11</v>
       </c>
-      <c r="C17" s="15">
+      <c r="C17" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D17" s="15">
+      <c r="D17" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="E17" s="21"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="15"/>
-      <c r="H17" s="17"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
-      <c r="L17" s="2"/>
-      <c r="M17" s="2"/>
-      <c r="N17" s="2"/>
-      <c r="O17" s="2"/>
-      <c r="P17" s="2"/>
-      <c r="Q17" s="2"/>
-      <c r="R17" s="2"/>
-      <c r="S17" s="2"/>
-      <c r="T17" s="2"/>
-    </row>
-    <row r="18" customHeight="1" spans="1:20">
+      <c r="F17" s="13"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="16"/>
+      <c r="I17" s="44"/>
+      <c r="J17" s="44"/>
+      <c r="K17" s="44"/>
+      <c r="L17" s="44"/>
+      <c r="M17" s="44"/>
+      <c r="N17" s="44"/>
+      <c r="O17" s="44"/>
+      <c r="P17" s="44"/>
+      <c r="Q17" s="44"/>
+      <c r="R17" s="44"/>
+      <c r="S17" s="44"/>
+      <c r="T17" s="44"/>
+    </row>
+    <row r="18" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18" s="18" t="s">
         <v>74</v>
       </c>
       <c r="B18" s="19">
         <v>12</v>
       </c>
-      <c r="C18" s="15">
+      <c r="C18" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D18" s="15">
+      <c r="D18" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4701,90 +3738,90 @@
         <f>SUM(H7:H16)</f>
         <v>0</v>
       </c>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
-      <c r="K18" s="2"/>
-      <c r="L18" s="2"/>
-      <c r="M18" s="2"/>
-      <c r="N18" s="2"/>
-      <c r="O18" s="2"/>
-      <c r="P18" s="2"/>
-      <c r="Q18" s="2"/>
-      <c r="R18" s="2"/>
-      <c r="S18" s="2"/>
-      <c r="T18" s="2"/>
-    </row>
-    <row r="19" customHeight="1" spans="1:20">
+      <c r="I18" s="44"/>
+      <c r="J18" s="44"/>
+      <c r="K18" s="44"/>
+      <c r="L18" s="44"/>
+      <c r="M18" s="44"/>
+      <c r="N18" s="44"/>
+      <c r="O18" s="44"/>
+      <c r="P18" s="44"/>
+      <c r="Q18" s="44"/>
+      <c r="R18" s="44"/>
+      <c r="S18" s="44"/>
+      <c r="T18" s="44"/>
+    </row>
+    <row r="19" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19" s="18" t="s">
         <v>78</v>
       </c>
       <c r="B19" s="19">
         <v>13</v>
       </c>
-      <c r="C19" s="15">
+      <c r="C19" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D19" s="15">
+      <c r="D19" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="E19" s="16" t="s">
+      <c r="E19" s="15" t="s">
         <v>81</v>
       </c>
       <c r="F19" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="G19" s="15"/>
-      <c r="H19" s="17"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
-      <c r="K19" s="2"/>
-      <c r="L19" s="2"/>
-      <c r="M19" s="2"/>
-      <c r="N19" s="2"/>
-      <c r="O19" s="2"/>
-      <c r="P19" s="2"/>
-      <c r="Q19" s="2"/>
-      <c r="R19" s="2"/>
-      <c r="S19" s="2"/>
-      <c r="T19" s="2"/>
-    </row>
-    <row r="20" customHeight="1" spans="1:20">
+      <c r="G19" s="14"/>
+      <c r="H19" s="16"/>
+      <c r="I19" s="44"/>
+      <c r="J19" s="44"/>
+      <c r="K19" s="44"/>
+      <c r="L19" s="44"/>
+      <c r="M19" s="44"/>
+      <c r="N19" s="44"/>
+      <c r="O19" s="44"/>
+      <c r="P19" s="44"/>
+      <c r="Q19" s="44"/>
+      <c r="R19" s="44"/>
+      <c r="S19" s="44"/>
+      <c r="T19" s="44"/>
+    </row>
+    <row r="20" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20" s="18" t="s">
         <v>82</v>
       </c>
       <c r="B20" s="19">
         <v>14</v>
       </c>
-      <c r="C20" s="15"/>
-      <c r="D20" s="15"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="14"/>
       <c r="E20" s="20" t="s">
         <v>81</v>
       </c>
       <c r="F20" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="G20" s="15" t="s">
+      <c r="G20" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="H20" s="17" t="s">
+      <c r="H20" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="2"/>
-      <c r="L20" s="2"/>
-      <c r="M20" s="2"/>
-      <c r="N20" s="2"/>
-      <c r="O20" s="2"/>
-      <c r="P20" s="2"/>
-      <c r="Q20" s="2"/>
-      <c r="R20" s="2"/>
-      <c r="S20" s="2"/>
-      <c r="T20" s="2"/>
-    </row>
-    <row r="21" customHeight="1" spans="1:20">
+      <c r="I20" s="44"/>
+      <c r="J20" s="44"/>
+      <c r="K20" s="44"/>
+      <c r="L20" s="44"/>
+      <c r="M20" s="44"/>
+      <c r="N20" s="44"/>
+      <c r="O20" s="44"/>
+      <c r="P20" s="44"/>
+      <c r="Q20" s="44"/>
+      <c r="R20" s="44"/>
+      <c r="S20" s="44"/>
+      <c r="T20" s="44"/>
+    </row>
+    <row r="21" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A21" s="24" t="s">
         <v>85</v>
       </c>
@@ -4805,67 +3842,67 @@
       <c r="F21" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="G21" s="15" t="s">
+      <c r="G21" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="H21" s="17" t="s">
+      <c r="H21" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
-      <c r="K21" s="2"/>
-      <c r="L21" s="2"/>
-      <c r="M21" s="2"/>
-      <c r="N21" s="2"/>
-      <c r="O21" s="2"/>
-      <c r="P21" s="2"/>
-      <c r="Q21" s="2"/>
-      <c r="R21" s="2"/>
-      <c r="S21" s="2"/>
-      <c r="T21" s="2"/>
-    </row>
-    <row r="22" customHeight="1" spans="1:20">
-      <c r="A22" s="13" t="s">
+      <c r="I21" s="44"/>
+      <c r="J21" s="44"/>
+      <c r="K21" s="44"/>
+      <c r="L21" s="44"/>
+      <c r="M21" s="44"/>
+      <c r="N21" s="44"/>
+      <c r="O21" s="44"/>
+      <c r="P21" s="44"/>
+      <c r="Q21" s="44"/>
+      <c r="R21" s="44"/>
+      <c r="S21" s="44"/>
+      <c r="T21" s="44"/>
+    </row>
+    <row r="22" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A22" s="12" t="s">
         <v>86</v>
       </c>
       <c r="B22" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="C22" s="15"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="16" t="s">
+      <c r="C22" s="14"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="15" t="s">
         <v>87</v>
       </c>
       <c r="F22" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="G22" s="15"/>
-      <c r="H22" s="17"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="2"/>
-      <c r="K22" s="2"/>
-      <c r="L22" s="2"/>
-      <c r="M22" s="2"/>
-      <c r="N22" s="2"/>
-      <c r="O22" s="2"/>
-      <c r="P22" s="2"/>
-      <c r="Q22" s="2"/>
-      <c r="R22" s="2"/>
-      <c r="S22" s="2"/>
-      <c r="T22" s="2"/>
-    </row>
-    <row r="23" customHeight="1" spans="1:20">
+      <c r="G22" s="14"/>
+      <c r="H22" s="16"/>
+      <c r="I22" s="44"/>
+      <c r="J22" s="44"/>
+      <c r="K22" s="44"/>
+      <c r="L22" s="44"/>
+      <c r="M22" s="44"/>
+      <c r="N22" s="44"/>
+      <c r="O22" s="44"/>
+      <c r="P22" s="44"/>
+      <c r="Q22" s="44"/>
+      <c r="R22" s="44"/>
+      <c r="S22" s="44"/>
+      <c r="T22" s="44"/>
+    </row>
+    <row r="23" ht="21" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A23" s="18" t="s">
         <v>88</v>
       </c>
       <c r="B23" s="19">
         <v>16</v>
       </c>
-      <c r="C23" s="15">
+      <c r="C23" s="14">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="D23" s="15">
+      <c r="D23" s="14">
         <f>0</f>
         <v>0</v>
       </c>
@@ -4875,39 +3912,39 @@
       <c r="F23" s="19">
         <v>42</v>
       </c>
-      <c r="G23" s="15">
+      <c r="G23" s="14">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="H23" s="17">
+      <c r="H23" s="16">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="I23" s="2"/>
-      <c r="J23" s="2"/>
-      <c r="K23" s="2"/>
-      <c r="L23" s="2"/>
-      <c r="M23" s="2"/>
-      <c r="N23" s="2"/>
-      <c r="O23" s="2"/>
-      <c r="P23" s="2"/>
-      <c r="Q23" s="2"/>
-      <c r="R23" s="2"/>
-      <c r="S23" s="2"/>
-      <c r="T23" s="2"/>
-    </row>
-    <row r="24" customHeight="1" spans="1:20">
+      <c r="I23" s="44"/>
+      <c r="J23" s="44"/>
+      <c r="K23" s="44"/>
+      <c r="L23" s="44"/>
+      <c r="M23" s="44"/>
+      <c r="N23" s="44"/>
+      <c r="O23" s="44"/>
+      <c r="P23" s="44"/>
+      <c r="Q23" s="44"/>
+      <c r="R23" s="44"/>
+      <c r="S23" s="44"/>
+      <c r="T23" s="44"/>
+    </row>
+    <row r="24" ht="21" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="18" t="s">
         <v>94</v>
       </c>
       <c r="B24" s="19">
         <v>17</v>
       </c>
-      <c r="C24" s="15">
+      <c r="C24" s="14">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="D24" s="15">
+      <c r="D24" s="14">
         <f>0</f>
         <v>0</v>
       </c>
@@ -4917,27 +3954,27 @@
       <c r="F24" s="19">
         <v>43</v>
       </c>
-      <c r="G24" s="15">
+      <c r="G24" s="14">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="H24" s="17">
+      <c r="H24" s="16">
         <f>0</f>
         <v>0</v>
       </c>
     </row>
-    <row r="25" customHeight="1" spans="1:20">
+    <row r="25" ht="21" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="18" t="s">
         <v>100</v>
       </c>
       <c r="B25" s="19">
         <v>18</v>
       </c>
-      <c r="C25" s="15">
+      <c r="C25" s="14">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="D25" s="15">
+      <c r="D25" s="14">
         <f>0</f>
         <v>0</v>
       </c>
@@ -4947,27 +3984,27 @@
       <c r="F25" s="19">
         <v>44</v>
       </c>
-      <c r="G25" s="15">
+      <c r="G25" s="14">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="H25" s="17">
+      <c r="H25" s="16">
         <f>0</f>
         <v>0</v>
       </c>
     </row>
-    <row r="26" customHeight="1" spans="1:20">
+    <row r="26" ht="21" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="18" t="s">
         <v>106</v>
       </c>
       <c r="B26" s="19">
         <v>19</v>
       </c>
-      <c r="C26" s="15">
+      <c r="C26" s="14">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="D26" s="15">
+      <c r="D26" s="14">
         <f>0</f>
         <v>0</v>
       </c>
@@ -4977,41 +4014,41 @@
       <c r="F26" s="19">
         <v>45</v>
       </c>
-      <c r="G26" s="15"/>
-      <c r="H26" s="17"/>
-    </row>
-    <row r="27" customHeight="1" spans="1:20">
+      <c r="G26" s="14"/>
+      <c r="H26" s="16"/>
+    </row>
+    <row r="27" ht="21" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="18" t="s">
         <v>110</v>
       </c>
       <c r="B27" s="19">
         <v>20</v>
       </c>
-      <c r="C27" s="15">
+      <c r="C27" s="14">
         <f>C25-C26</f>
         <v>0</v>
       </c>
-      <c r="D27" s="15">
+      <c r="D27" s="14">
         <f>D25-D26</f>
         <v>0</v>
       </c>
       <c r="E27" s="21"/>
-      <c r="F27" s="14"/>
+      <c r="F27" s="13"/>
       <c r="G27" s="25"/>
       <c r="H27" s="26"/>
     </row>
-    <row r="28" customHeight="1" spans="1:20">
+    <row r="28" ht="21" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="18" t="s">
         <v>111</v>
       </c>
       <c r="B28" s="19">
         <v>21</v>
       </c>
-      <c r="C28" s="15">
+      <c r="C28" s="14">
         <f t="shared" ref="C28:C35" si="4">0</f>
         <v>0</v>
       </c>
-      <c r="D28" s="15">
+      <c r="D28" s="14">
         <f t="shared" ref="D28:D35" si="5">0</f>
         <v>0</v>
       </c>
@@ -5030,18 +4067,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" customHeight="1" spans="1:20">
+    <row r="29" ht="21" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="18" t="s">
         <v>115</v>
       </c>
       <c r="B29" s="19">
         <v>22</v>
       </c>
-      <c r="C29" s="15">
+      <c r="C29" s="14">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="D29" s="15">
+      <c r="D29" s="14">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -5060,66 +4097,66 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" customHeight="1" spans="1:20">
+    <row r="30" ht="21" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="18" t="s">
         <v>119</v>
       </c>
       <c r="B30" s="19">
         <v>23</v>
       </c>
-      <c r="C30" s="15">
+      <c r="C30" s="14">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="D30" s="15">
+      <c r="D30" s="14">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="E30" s="16" t="s">
+      <c r="E30" s="15" t="s">
         <v>81</v>
       </c>
       <c r="F30" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="G30" s="15"/>
-      <c r="H30" s="17"/>
-    </row>
-    <row r="31" customHeight="1" spans="1:20">
+      <c r="G30" s="14"/>
+      <c r="H30" s="16"/>
+    </row>
+    <row r="31" ht="21" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="18" t="s">
         <v>122</v>
       </c>
       <c r="B31" s="19">
         <v>24</v>
       </c>
-      <c r="C31" s="15">
+      <c r="C31" s="14">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="D31" s="15">
+      <c r="D31" s="14">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="E31" s="16" t="s">
+      <c r="E31" s="15" t="s">
         <v>125</v>
       </c>
       <c r="F31" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="G31" s="15"/>
-      <c r="H31" s="17"/>
-    </row>
-    <row r="32" customHeight="1" spans="1:20">
+      <c r="G31" s="14"/>
+      <c r="H31" s="16"/>
+    </row>
+    <row r="32" ht="21" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
         <v>126</v>
       </c>
       <c r="B32" s="19">
         <v>25</v>
       </c>
-      <c r="C32" s="15">
+      <c r="C32" s="14">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="D32" s="15">
+      <c r="D32" s="14">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -5129,27 +4166,27 @@
       <c r="F32" s="19">
         <v>48</v>
       </c>
-      <c r="G32" s="15">
+      <c r="G32" s="14">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="H32" s="17">
+      <c r="H32" s="16">
         <f>0</f>
         <v>0</v>
       </c>
     </row>
-    <row r="33" customHeight="1" spans="1:8">
+    <row r="33" ht="21" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="18" t="s">
         <v>132</v>
       </c>
       <c r="B33" s="19">
         <v>26</v>
       </c>
-      <c r="C33" s="15">
+      <c r="C33" s="14">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="D33" s="15">
+      <c r="D33" s="14">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -5159,27 +4196,27 @@
       <c r="F33" s="19">
         <v>49</v>
       </c>
-      <c r="G33" s="15">
+      <c r="G33" s="14">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="H33" s="17">
+      <c r="H33" s="16">
         <f>0</f>
         <v>0</v>
       </c>
     </row>
-    <row r="34" customHeight="1" spans="1:8">
+    <row r="34" ht="21" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
         <v>138</v>
       </c>
       <c r="B34" s="19">
         <v>27</v>
       </c>
-      <c r="C34" s="15">
+      <c r="C34" s="14">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="D34" s="15">
+      <c r="D34" s="14">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -5189,27 +4226,27 @@
       <c r="F34" s="19">
         <v>50</v>
       </c>
-      <c r="G34" s="15">
+      <c r="G34" s="14">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="H34" s="17">
+      <c r="H34" s="16">
         <f>0</f>
         <v>0</v>
       </c>
     </row>
-    <row r="35" customHeight="1" spans="1:8">
+    <row r="35" ht="21" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="18" t="s">
         <v>144</v>
       </c>
       <c r="B35" s="19">
         <v>28</v>
       </c>
-      <c r="C35" s="15">
+      <c r="C35" s="14">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="D35" s="15">
+      <c r="D35" s="14">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -5219,30 +4256,30 @@
       <c r="F35" s="19">
         <v>51</v>
       </c>
-      <c r="G35" s="15">
+      <c r="G35" s="14">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="H35" s="17">
+      <c r="H35" s="16">
         <f>0</f>
         <v>0</v>
       </c>
     </row>
-    <row r="36" customHeight="1" spans="1:8">
+    <row r="36" ht="21" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="27"/>
       <c r="B36" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="C36" s="15"/>
-      <c r="D36" s="15"/>
+      <c r="C36" s="14"/>
+      <c r="D36" s="14"/>
       <c r="E36" s="28"/>
       <c r="F36" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="G36" s="15"/>
-      <c r="H36" s="17"/>
-    </row>
-    <row r="37" customHeight="1" spans="1:8">
+      <c r="G36" s="14"/>
+      <c r="H36" s="16"/>
+    </row>
+    <row r="37" ht="21" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="24" t="s">
         <v>150</v>
       </c>
@@ -5272,7 +4309,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" customHeight="1" spans="1:8">
+    <row r="38" ht="21" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="29" t="s">
         <v>152</v>
       </c>
@@ -5303,7 +4340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" customHeight="1" spans="1:8">
+    <row r="39" ht="21" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="33"/>
       <c r="B39" s="34"/>
       <c r="C39" s="35"/>
@@ -5313,7 +4350,7 @@
       <c r="G39" s="35"/>
       <c r="H39" s="35"/>
     </row>
-    <row r="40" customHeight="1" spans="1:8">
+    <row r="40" ht="21" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="36" t="s">
         <v>154</v>
       </c>
@@ -5331,7 +4368,7 @@
       </c>
       <c r="H40" s="1"/>
     </row>
-    <row r="41" customHeight="1" spans="1:8">
+    <row r="41" ht="21" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -5341,26 +4378,25 @@
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
     </row>
-    <row r="42" customHeight="1" spans="1:8">
-      <c r="A42" s="37" t="s">
+    <row r="42" ht="21" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="43" t="s">
         <v>158</v>
       </c>
-      <c r="B42" s="37"/>
-      <c r="C42" s="37" t="s">
+      <c r="B42" s="43"/>
+      <c r="C42" s="43" t="s">
         <v>159</v>
       </c>
-      <c r="D42" s="37"/>
-      <c r="E42" s="37" t="s">
+      <c r="D42" s="43"/>
+      <c r="E42" s="43" t="s">
         <v>160</v>
       </c>
-      <c r="F42" s="37"/>
-      <c r="G42" s="37" t="s">
+      <c r="F42" s="43"/>
+      <c r="G42" s="43" t="s">
         <v>161</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.74999998873613" right="0.74999998873613" top="0" bottom="0" header="0.499999992490753" footer="0.499999992490753"/>
-  <pageSetup paperSize="1" orientation="landscape" horizontalDpi="600" verticalDpi="600"/>
-  <headerFooter alignWithMargins="0" scaleWithDoc="0"/>
+  <pageSetup paperSize="1" orientation="landscape" horizontalDpi="600" verticalDpi="600" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>